--- a/02_DIA_inicio_2026_analisis_assets/rbd_9703_escuela-esperanza-joven_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9703_escuela-esperanza-joven_nt1_rubricas.xlsx
@@ -1800,13 +1800,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04880CC4-01C9-4C2D-AE2E-270A515660AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1212FCAD-3943-46CE-9C32-1D6F9B32CD40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C207364F-22BC-4AE1-B257-52C0E64217A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88F4C2E7-E76D-4E62-805D-3EC850D6B2B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D7F5CE6-029B-4EBC-8FDB-D33AC6E10F62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEE14311-0F1C-46C0-9743-8D8E6D8760C7}"/>
 </file>